--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="97">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,27 +260,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de l'entrée. L'entrée Traitement doit être identifiée de manière unique</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Acte ou situation</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement.note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Partie narrative de l’entrée</t>
+    <t>Identifiant</t>
   </si>
   <si>
     <t>fr-lm-traitement.status</t>
@@ -290,10 +270,10 @@
 </t>
   </si>
   <si>
-    <t>Statut de l’entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement.occurancePeriod</t>
+    <t>Statut, completed</t>
+  </si>
+  <si>
+    <t>fr-lm-traitement.dureeTraitement</t>
   </si>
   <si>
     <t xml:space="preserve">dateTime
@@ -303,69 +283,14 @@
     <t>Durée du traitement</t>
   </si>
   <si>
-    <t>fr-lm-traitement.occuranceDateTim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
+    <t>fr-lm-traitement.dosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-posologie
 </t>
   </si>
   <si>
-    <t>Fréquence d'administration</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement.dosage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base
-</t>
-  </si>
-  <si>
-    <t>Dosage</t>
-  </si>
-  <si>
-    <t>SNOMED CT (2.16.840.1.113883.6.96)</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement.dosage.route</t>
-  </si>
-  <si>
-    <t>Voie d'administration</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement.dosage.site</t>
-  </si>
-  <si>
-    <t>Région anatomique d'administration</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement.dosage.dose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>Dose à administrer</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement.dosage.rate[x]</t>
-  </si>
-  <si>
-    <t>Ratio
-Quantity</t>
-  </si>
-  <si>
-    <t>Rythme d'administration</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement.dosage.doseMaximale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratio
-</t>
-  </si>
-  <si>
-    <t>Dose maximale</t>
+    <t>Posologie</t>
   </si>
   <si>
     <t>fr-lm-traitement.medicament</t>
@@ -378,50 +303,14 @@
     <t>Médicament</t>
   </si>
   <si>
-    <t>fr-lm-traitement.reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-reference-interne
-</t>
+    <t>fr-lm-traitement.reason[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+http://hl7.org/cda/stds/core/StructureDefinition/Reference</t>
   </si>
   <si>
     <t>Motif du traitement</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement.prescription</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-prescription-entree
-</t>
-  </si>
-  <si>
-    <t>Prescription</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement.subordinateTreatment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-traitement-subordonne
-</t>
-  </si>
-  <si>
-    <t>Traitement subordonné</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement.instructionsPatient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-instructions-patient
-</t>
-  </si>
-  <si>
-    <t>Instruction au patient</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement.precondition</t>
-  </si>
-  <si>
-    <t>Précondition</t>
   </si>
 </sst>
 </file>
@@ -723,11 +612,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ20"/>
+  <dimension ref="A1:AJ8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="31.71484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="31.71484375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="27.328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -736,7 +625,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="77.03515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="69.35546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -750,14 +639,14 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="31.14453125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="31.71484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="27.328125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1086,7 +975,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>79</v>
@@ -1161,7 +1050,7 @@
         <v>82</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
         <v>79</v>
@@ -1186,7 +1075,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>79</v>
@@ -1261,7 +1150,7 @@
         <v>85</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>79</v>
@@ -1286,7 +1175,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>79</v>
@@ -1361,7 +1250,7 @@
         <v>88</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
         <v>79</v>
@@ -1386,7 +1275,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>79</v>
@@ -1461,7 +1350,7 @@
         <v>91</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
         <v>79</v>
@@ -1489,7 +1378,7 @@
         <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -1564,1212 +1453,12 @@
         <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q9" s="2"/>
-      <c r="R9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ9" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AG10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ10" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K12" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K13" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K14" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K17" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q17" s="2"/>
-      <c r="R17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G18" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K18" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q18" s="2"/>
-      <c r="R18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K19" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q19" s="2"/>
-      <c r="R19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K20" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q20" s="2"/>
-      <c r="R20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
